--- a/02. Planificacion/Backlog Detallado del Producto.xlsx
+++ b/02. Planificacion/Backlog Detallado del Producto.xlsx
@@ -1560,7 +1560,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N10" s="9"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N11" s="9"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N12" s="9"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N13" s="9"/>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N14" s="9"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N15" s="9"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N16" s="9"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N17" s="9"/>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N18" s="9"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N19" s="9"/>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N20" s="9"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N21" s="9"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N22" s="9"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N23" s="9"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N24" s="9"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="N25" s="9"/>
